--- a/data/trans_dic/P44A$analisis-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P44A$analisis-Edad-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos un análisis de sangre para detectar cáncer de cólon</t>
+          <t>Población a la que le han realizado al menos un análisis de sangre para detectar cáncer de cólon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -615,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>16-24</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -625,47 +625,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,16%</t>
         </is>
       </c>
     </row>
@@ -678,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>15,31; 74,51</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19,76; 58,42</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11,01; 94,51</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>16,02; 58,77</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,9; 16,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>25,65; 60,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,22; 41,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,64; 90,63</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -735,47 +735,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -788,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18,22; 50,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>19,4; 46,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,47; 20,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,69; 43,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20,36; 53,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,14; 13,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18,46; 40,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>23,95; 44,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,33; 15,43</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>65-74</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -845,47 +845,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -898,54 +898,54 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,66; 55,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>27,74; 58,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,9; 19,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15,79; 51,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,77; 49,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,41; 16,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20,97; 45,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>27,88; 50,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,52; 16,56</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>75 o más</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -955,47 +955,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -1008,54 +1008,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,47; 77,3</t>
+          <t>29,5; 67,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,95; 58,67</t>
+          <t>22,78; 52,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,65; 94,73</t>
+          <t>5,73; 15,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,54; 59,19</t>
+          <t>16,57; 63,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>25,82; 64,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 17,24</t>
+          <t>9,0; 18,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,43; 58,25</t>
+          <t>28,15; 56,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,98; 42,26</t>
+          <t>28,76; 51,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,57; 92,59</t>
+          <t>8,51; 15,46</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1065,47 +1065,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -1118,389 +1118,59 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,41; 48,4</t>
+          <t>27,93; 49,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,12; 45,75</t>
+          <t>29,47; 44,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,73; 19,42</t>
+          <t>12,46; 74,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,94; 44,84</t>
+          <t>22,85; 42,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,48; 52,4</t>
+          <t>24,92; 44,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,37; 13,85</t>
+          <t>9,3; 13,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,71; 42,65</t>
+          <t>27,99; 42,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23,9; 44,29</t>
+          <t>29,07; 41,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,16; 15,27</t>
+          <t>11,86; 62,71</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>65-74</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>33,66%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>42,11%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>13,74%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>31,97%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>32,3%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>12,52%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>32,81%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>38,04%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>13,17%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n"/>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>16,76; 54,81</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>28,68; 60,14</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>9,66; 18,67</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>16,39; 50,02</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>18,6; 50,48</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>9,01; 16,91</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>21,08; 47,43</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>27,41; 51,2</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>10,32; 16,42</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>46,66%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>36,24%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>10,42%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>36,96%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>43,62%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>13,19%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>42,22%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>39,91%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>11,88%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>29,39; 67,14</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>20,57; 50,87</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>6,35; 16,66</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>16,09; 59,6</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>24,18; 61,27</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>9,03; 18,75</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>28,02; 58,32</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>28,93; 51,93</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>8,79; 15,64</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>37,55%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>36,47%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>40,68%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>31,58%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>34,0%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>11,28%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>34,6%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>35,43%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>29,48%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>27,99; 47,61</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>29,1; 44,33</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>12,88; 74,31</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>23,71; 41,96</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>25,43; 44,45</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>9,24; 13,41</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>28,24; 41,87</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>29,93; 41,98</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>11,88; 60,49</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="9">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
@@ -1508,11 +1178,8 @@
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A14:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1524,7 +1191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1543,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos un análisis de sangre para detectar cáncer de cólon</t>
+          <t>Población a la que le han realizado al menos un análisis de sangre para detectar cáncer de cólon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1634,7 +1301,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>16-24</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1644,47 +1311,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1697,47 +1364,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6620</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9896</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>256815</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7657</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6853</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14277</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9896</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>263668</t>
         </is>
       </c>
     </row>
@@ -1750,54 +1417,54 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2170; 10559</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5293; 15647</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>36677; 314865</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3285; 12053</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3501; 11800</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8896; 20971</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5376; 15743</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>43059; 366736</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1807,47 +1474,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>57</t>
         </is>
       </c>
     </row>
@@ -1860,47 +1527,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12368</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16587</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26583</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13683</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14949</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20579</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>30271</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>41532</t>
         </is>
       </c>
     </row>
@@ -1913,54 +1580,54 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7166; 19679</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10165; 24367</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>19178; 37268</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3947; 14637</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7702; 20336</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9561; 20511</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13499; 29655</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>21612; 40406</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>31630; 52317</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>65-74</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1970,47 +1637,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>67</t>
         </is>
       </c>
     </row>
@@ -2023,47 +1690,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10306</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18492</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22515</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10033</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17907</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20339</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28568</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>40422</t>
         </is>
       </c>
     </row>
@@ -2076,54 +1743,54 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5099; 16842</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12181; 25598</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16226; 31495</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4956; 16210</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5231; 15454</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13465; 24086</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13004; 28377</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20942; 37573</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>32299; 50819</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>75 o más</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2133,47 +1800,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -2186,47 +1853,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>11777</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9896</t>
+          <t>13264</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>256815</t>
+          <t>10055</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7657</t>
+          <t>7871</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15729</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6853</t>
+          <t>14215</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14277</t>
+          <t>19648</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9896</t>
+          <t>28993</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>263668</t>
+          <t>24271</t>
         </is>
       </c>
     </row>
@@ -2239,54 +1906,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3043; 10955</t>
+          <t>7445; 17132</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5344; 15713</t>
+          <t>8335; 19155</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38816; 315630</t>
+          <t>5530; 15424</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3391; 12139</t>
+          <t>3528; 13560</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1885</t>
+          <t>9309; 23268</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3451; 12320</t>
+          <t>9704; 19810</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8473; 20201</t>
+          <t>13099; 26439</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5287; 15983</t>
+          <t>20897; 37448</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>42787; 374689</t>
+          <t>17384; 31581</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2296,47 +1963,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>58</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>87</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>101</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>188</t>
         </is>
       </c>
     </row>
@@ -2349,47 +2016,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12368</t>
+          <t>41070</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16587</t>
+          <t>58240</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26583</t>
+          <t>315969</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>33771</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13683</t>
+          <t>39488</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14949</t>
+          <t>53924</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20579</t>
+          <t>74842</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>30271</t>
+          <t>97728</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>41532</t>
+          <t>369892</t>
         </is>
       </c>
     </row>
@@ -2402,559 +2069,67 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6850; 19041</t>
+          <t>30546; 53643</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10019; 23971</t>
+          <t>47067; 71353</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17833; 35578</t>
+          <t>96806; 574811</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3355; 15139</t>
+          <t>24440; 45004</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7373; 19827</t>
+          <t>28939; 51378</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9916; 21575</t>
+          <t>44454; 64367</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13675; 31181</t>
+          <t>60545; 90964</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>21563; 39962</t>
+          <t>80188; 113112</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>31044; 51764</t>
+          <t>148812; 786892</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>65-74</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n"/>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>10306</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>18492</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>22515</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>10033</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>10076</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>17907</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>20339</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>28568</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>40422</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n"/>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>5130; 16781</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>12595; 26408</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>15831; 30584</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>5145; 15699</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>5803; 15747</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>12883; 24192</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>13068; 29404</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>20582; 38450</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>31666; 50402</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>11777</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>13264</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>10055</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>7871</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>15729</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>14215</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>19648</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>28993</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>24271</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>7418; 16947</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>7530; 18617</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>6124; 16071</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>3426; 12693</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>8720; 22093</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>9735; 20211</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>13041; 27141</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>21016; 37731</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>17944; 31955</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n"/>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>41070</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>58240</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>315969</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>33771</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>39488</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>53924</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>74842</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>97728</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>369892</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n"/>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>30607; 52072</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>46469; 70793</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>100031; 577175</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>25357; 44873</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>29533; 51612</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>44190; 64092</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>61085; 90565</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>82559; 115787</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>149064; 759094</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="9">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A25:A27"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P44A$analisis-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P44A$analisis-Edad-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -678,22 +678,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,31; 74,51</t>
+          <t>19,49; 76,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,76; 58,42</t>
+          <t>19,48; 58,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,01; 94,51</t>
+          <t>7,7; 23,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,02; 58,77</t>
+          <t>16,53; 63,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -703,22 +703,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,9; 16,51</t>
+          <t>5,44; 17,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,65; 60,47</t>
+          <t>24,24; 58,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,22; 41,63</t>
+          <t>11,72; 43,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,64; 90,63</t>
+          <t>7,96; 17,75</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,22; 50,02</t>
+          <t>17,39; 48,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,4; 46,51</t>
+          <t>19,54; 47,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,47; 20,34</t>
+          <t>9,69; 19,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,69; 43,35</t>
+          <t>10,45; 44,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,36; 53,74</t>
+          <t>20,01; 55,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,14; 13,17</t>
+          <t>7,18; 14,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,46; 40,57</t>
+          <t>17,62; 40,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,95; 44,78</t>
+          <t>23,34; 44,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,33; 15,43</t>
+          <t>9,43; 15,33</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,66; 55,01</t>
+          <t>16,94; 56,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,74; 58,29</t>
+          <t>27,1; 58,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,9; 19,22</t>
+          <t>9,93; 18,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,79; 51,65</t>
+          <t>18,11; 49,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,77; 49,54</t>
+          <t>18,81; 51,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,41; 16,84</t>
+          <t>9,5; 17,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,97; 45,77</t>
+          <t>21,08; 47,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27,88; 50,03</t>
+          <t>26,66; 49,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,52; 16,56</t>
+          <t>10,44; 16,73</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,5; 67,88</t>
+          <t>26,22; 67,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,78; 52,34</t>
+          <t>22,89; 51,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,73; 15,99</t>
+          <t>6,05; 16,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,57; 63,68</t>
+          <t>16,69; 59,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,82; 64,53</t>
+          <t>25,12; 62,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,0; 18,38</t>
+          <t>8,82; 18,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,15; 56,81</t>
+          <t>29,15; 57,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28,76; 51,54</t>
+          <t>29,71; 51,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,51; 15,46</t>
+          <t>8,89; 16,15</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,93; 49,05</t>
+          <t>28,55; 47,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,47; 44,68</t>
+          <t>29,02; 44,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,46; 74,0</t>
+          <t>10,82; 16,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,85; 42,08</t>
+          <t>22,73; 42,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,92; 44,24</t>
+          <t>25,02; 43,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,3; 13,46</t>
+          <t>9,68; 13,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,99; 42,05</t>
+          <t>27,88; 41,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>29,07; 41,01</t>
+          <t>29,82; 41,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,86; 62,71</t>
+          <t>10,92; 14,19</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>256815</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6853</t>
+          <t>7720</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>263668</t>
+          <t>21192</t>
         </is>
       </c>
     </row>
@@ -1417,22 +1417,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2170; 10559</t>
+          <t>2762; 10806</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5293; 15647</t>
+          <t>5217; 15591</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36677; 314865</t>
+          <t>7316; 21982</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3285; 12053</t>
+          <t>3390; 12930</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1442,22 +1442,22 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3501; 11800</t>
+          <t>4171; 13156</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8896; 20971</t>
+          <t>8405; 20173</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5376; 15743</t>
+          <t>4434; 16593</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>43059; 366736</t>
+          <t>13677; 30476</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26583</t>
+          <t>26909</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14949</t>
+          <t>17828</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>41532</t>
+          <t>44738</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7166; 19679</t>
+          <t>6843; 19051</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10165; 24367</t>
+          <t>10239; 24709</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19178; 37268</t>
+          <t>18763; 36910</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3947; 14637</t>
+          <t>3528; 14927</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7702; 20336</t>
+          <t>7570; 20874</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9561; 20511</t>
+          <t>12535; 26002</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13499; 29655</t>
+          <t>12882; 29718</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21612; 40406</t>
+          <t>21059; 40410</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31630; 52317</t>
+          <t>34725; 56446</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22515</t>
+          <t>24627</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17907</t>
+          <t>20670</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40422</t>
+          <t>45297</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5099; 16842</t>
+          <t>5185; 17285</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12181; 25598</t>
+          <t>11900; 25720</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16226; 31495</t>
+          <t>17634; 33410</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4956; 16210</t>
+          <t>5683; 15673</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5231; 15454</t>
+          <t>5868; 15909</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13465; 24086</t>
+          <t>14971; 28186</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13004; 28377</t>
+          <t>13069; 29324</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20942; 37573</t>
+          <t>20021; 37362</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>32299; 50819</t>
+          <t>34990; 56087</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10055</t>
+          <t>11138</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14215</t>
+          <t>15859</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>24271</t>
+          <t>26998</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7445; 17132</t>
+          <t>6617; 17124</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8335; 19155</t>
+          <t>8376; 19011</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5530; 15424</t>
+          <t>6330; 17394</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3528; 13560</t>
+          <t>3554; 12710</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9309; 23268</t>
+          <t>9056; 22706</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9704; 19810</t>
+          <t>10531; 22249</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13099; 26439</t>
+          <t>13565; 26913</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20897; 37448</t>
+          <t>21582; 37490</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17384; 31581</t>
+          <t>19930; 36182</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>315969</t>
+          <t>76147</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53924</t>
+          <t>62077</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>369892</t>
+          <t>138224</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>30546; 53643</t>
+          <t>31229; 52413</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>47067; 71353</t>
+          <t>46341; 70995</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96806; 574811</t>
+          <t>61756; 94022</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24440; 45004</t>
+          <t>24308; 45114</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>28939; 51378</t>
+          <t>29060; 50732</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44454; 64367</t>
+          <t>51114; 73872</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>60545; 90964</t>
+          <t>60319; 89254</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>80188; 113112</t>
+          <t>82236; 114733</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>148812; 786892</t>
+          <t>120008; 155990</t>
         </is>
       </c>
     </row>
